--- a/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -805,13 +805,13 @@
   <x:cols>
     <x:col min="1" max="1" width="3.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.567768" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="6.567768" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.853482" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15.853482" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.139196" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="3.710625" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="13.853482" style="0" customWidth="1"/>
   </x:cols>
@@ -973,13 +973,13 @@
   <x:cols>
     <x:col min="1" max="1" width="3.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.567768" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="6.567768" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.853482" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15.853482" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.139196" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="3.710625" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="13.853482" style="0" customWidth="1"/>
   </x:cols>
@@ -1147,11 +1147,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.282054" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8.424911" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.424911" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.567768" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="7.996339" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">

--- a/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -946,7 +946,7 @@
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
-      <x:c r="I9" s="0">
+      <x:c r="I9" s="0" t="str">
         <x:f>CONCATENATE("Count: ", CountA(Headers[Table Headers]))</x:f>
       </x:c>
     </x:row>
@@ -1114,7 +1114,7 @@
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
-      <x:c r="I9" s="0">
+      <x:c r="I9" s="0" t="str">
         <x:f>CONCATENATE("Count: ", CountA(Headers[Table Headers]))</x:f>
       </x:c>
     </x:row>

--- a/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -1149,7 +1149,7 @@
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="7.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="8.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="7.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.139196" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="8.710625" style="0" customWidth="1"/>
   </x:cols>
